--- a/feature.xlsx
+++ b/feature.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25440" windowHeight="10540"/>
+    <workbookView windowWidth="23360" windowHeight="8880"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="159">
   <si>
     <t>特征名</t>
   </si>
@@ -492,6 +492,18 @@
   </si>
   <si>
     <t>重度感染/脓毒症</t>
+  </si>
+  <si>
+    <t>B_RBC</t>
+  </si>
+  <si>
+    <t>&lt;3.5</t>
+  </si>
+  <si>
+    <t>3.5–5.5</t>
+  </si>
+  <si>
+    <t>&gt;5.5</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1134,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1137,6 +1149,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1477,7 +1498,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="17.6" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
@@ -2416,7 +2437,7 @@
         <v>149</v>
       </c>
       <c r="C56">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D56" t="s">
         <v>18</v>
@@ -2434,7 +2455,7 @@
         <v>151</v>
       </c>
       <c r="C57">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D57" t="s">
         <v>28</v>
@@ -2449,7 +2470,7 @@
         <v>153</v>
       </c>
       <c r="C58">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D58" t="s">
         <v>31</v>
@@ -2458,8 +2479,46 @@
         <v>154</v>
       </c>
     </row>
+    <row r="59" ht="18" spans="1:6">
+      <c r="A59" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C59" s="6">
+        <v>0</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="60" ht="18" spans="1:6">
+      <c r="A60" s="7"/>
+      <c r="B60" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C60" s="6">
+        <v>1</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="61" ht="18" spans="1:6">
+      <c r="A61" s="7"/>
+      <c r="B61" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C61" s="6">
+        <v>2</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="21">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A7:A9"/>
@@ -2480,6 +2539,7 @@
     <mergeCell ref="A50:A52"/>
     <mergeCell ref="A53:A55"/>
     <mergeCell ref="A56:A58"/>
+    <mergeCell ref="A59:A61"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
